--- a/ProyectoSoftwareSistemas/bin/Debug/output/sec1_ArchivoIntermedio.xlsx
+++ b/ProyectoSoftwareSistemas/bin/Debug/output/sec1_ArchivoIntermedio.xlsx
@@ -117,7 +117,7 @@
     <x:t>4</x:t>
   </x:si>
   <x:si>
-    <x:t>69100000</x:t>
+    <x:t>69100000*SE</x:t>
   </x:si>
   <x:si>
     <x:t>0007</x:t>
@@ -138,7 +138,7 @@
     <x:t>Simple</x:t>
   </x:si>
   <x:si>
-    <x:t>2F100000</x:t>
+    <x:t>2F100000*SE</x:t>
   </x:si>
   <x:si>
     <x:t>000B</x:t>
@@ -153,7 +153,7 @@
     <x:t>Indexado</x:t>
   </x:si>
   <x:si>
-    <x:t>0F900000</x:t>
+    <x:t>0F900000*SE</x:t>
   </x:si>
   <x:si>
     <x:t>000F</x:t>
@@ -210,7 +210,10 @@
     <x:t>LDB</x:t>
   </x:si>
   <x:si>
-    <x:t>690000</x:t>
+    <x:t>Error: Símbolos externos requieren Formato 4 (+)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>693FFF</x:t>
   </x:si>
   <x:si>
     <x:t>0006</x:t>
@@ -228,7 +231,7 @@
     <x:t>COUNT-TABLE+NUM1</x:t>
   </x:si>
   <x:si>
-    <x:t>FFFFFD</x:t>
+    <x:t>FFFFFD*SE</x:t>
   </x:si>
   <x:si>
     <x:t>1018</x:t>
@@ -240,13 +243,13 @@
     <x:t>HPROG  000000001018</x:t>
   </x:si>
   <x:si>
-    <x:t>T00000012050000691000002F1000000F9000001BA003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>T00000003690000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>T00100603FFFFFD</x:t>
+    <x:t>T0000001605000069100000*SE2F100000*SE0F900000*SE1BA003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>T00000003693FFF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>T00100604FFFFFD*SE</x:t>
   </x:si>
   <x:si>
     <x:t>E000000</x:t>
@@ -276,22 +279,22 @@
     <x:t>Tipo</x:t>
   </x:si>
   <x:si>
-    <x:t>Relativo</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Bloque</x:t>
+    <x:t>NumBloq</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SimboloExterno</x:t>
   </x:si>
   <x:si>
     <x:t>E</x:t>
   </x:si>
   <x:si>
+    <x:t>Sí</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R</x:t>
+  </x:si>
+  <x:si>
     <x:t>No</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sí</x:t>
   </x:si>
   <x:si>
     <x:t>1009</x:t>
@@ -656,8 +659,8 @@
     <x:col min="6" max="6" width="20.567768" style="0" customWidth="1"/>
     <x:col min="7" max="7" width="9.710625" style="0" customWidth="1"/>
     <x:col min="8" max="8" width="10.139196" style="0" customWidth="1"/>
-    <x:col min="9" max="9" width="23.282054" style="0" customWidth="1"/>
-    <x:col min="10" max="10" width="9.282054" style="0" customWidth="1"/>
+    <x:col min="9" max="9" width="44.853482" style="0" customWidth="1"/>
+    <x:col min="10" max="10" width="12.567768" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:10">
@@ -1198,10 +1201,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="I17" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="J17" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:10">
@@ -1244,10 +1247,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="C19" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D19" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E19" s="0" t="s">
         <x:v>54</x:v>
@@ -1276,16 +1279,16 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="C20" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D20" s="0" t="s">
         <x:v>57</x:v>
       </x:c>
       <x:c r="E20" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="F20" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="G20" s="0" t="s">
         <x:v>14</x:v>
@@ -1297,7 +1300,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="J20" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:10">
@@ -1308,13 +1311,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="C21" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D21" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E21" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="F21" s="0" t="s">
         <x:v>22</x:v>
@@ -1349,32 +1352,32 @@
   <x:dimension ref="A1:A5"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="48.853482" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="58.424911" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:1">
       <x:c r="A1" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:1">
       <x:c r="A2" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>74</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:1">
       <x:c r="A3" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>75</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:1">
       <x:c r="A4" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:1">
       <x:c r="A5" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1401,16 +1404,16 @@
   <x:sheetData>
     <x:row r="1" spans="1:4">
       <x:c r="A1" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B1" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C1" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D1" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>81</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:4">
@@ -1418,10 +1421,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
         <x:v>10</x:v>
@@ -1447,25 +1450,25 @@
     <x:col min="1" max="1" width="8.282054" style="0" customWidth="1"/>
     <x:col min="2" max="2" width="9.139196" style="0" customWidth="1"/>
     <x:col min="3" max="3" width="4.710625" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="8.139196" style="0" customWidth="1"/>
-    <x:col min="5" max="5" width="8.853482" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="9.282054" style="0" customWidth="1"/>
+    <x:col min="5" max="5" width="15.139196" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:5">
       <x:c r="A1" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B1" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C1" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D1" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="E1" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>87</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:5">
@@ -1476,30 +1479,30 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E2" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>89</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:5">
       <x:c r="A3" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E3" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>89</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:5">
@@ -1510,13 +1513,13 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E4" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>89</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:5">
@@ -1527,13 +1530,13 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>91</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:5">
@@ -1544,13 +1547,13 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E6" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>91</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:5">
@@ -1561,13 +1564,13 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>91</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:5">
@@ -1578,13 +1581,13 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E8" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>91</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1611,16 +1614,16 @@
   <x:sheetData>
     <x:row r="1" spans="1:4">
       <x:c r="A1" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B1" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C1" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D1" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>81</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:4">
@@ -1628,10 +1631,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
         <x:v>10</x:v>
@@ -1657,25 +1660,25 @@
     <x:col min="1" max="1" width="8.282054" style="0" customWidth="1"/>
     <x:col min="2" max="2" width="9.139196" style="0" customWidth="1"/>
     <x:col min="3" max="3" width="4.710625" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="8.139196" style="0" customWidth="1"/>
-    <x:col min="5" max="5" width="8.853482" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="9.282054" style="0" customWidth="1"/>
+    <x:col min="5" max="5" width="15.139196" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:5">
       <x:c r="A1" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B1" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C1" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D1" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="E1" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>87</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:5">
@@ -1686,13 +1689,13 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E2" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>89</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:5">
@@ -1703,13 +1706,13 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E3" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>89</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:5">
@@ -1720,30 +1723,30 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E4" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>91</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:5">
       <x:c r="A5" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="B5" s="0" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="B5" s="0" t="s">
-        <x:v>64</x:v>
-      </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>91</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:5">
@@ -1751,16 +1754,16 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E6" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>91</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
